--- a/sourcedata/Dim_MasterCustomer.xlsx
+++ b/sourcedata/Dim_MasterCustomer.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P57"/>
+  <dimension ref="A1:P107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -438,7 +438,7 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1826600539</t>
+          <t>1339670711</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>PSYCHIATRY</t>
+          <t>NEUROLOGY</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>9035 Main St</t>
+          <t>2386 Elm St</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>87397</t>
+          <t>23434</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -618,52 +618,52 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1702632297</t>
+          <t>1553035110</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Walker</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MD. Jessica Johnson</t>
+          <t>DO. Nancy Walker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>PSYCHIATRY</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3357 Elm St</t>
+          <t>620 Main St</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>95181</t>
+          <t>22280</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -698,52 +698,52 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1849621470</t>
+          <t>1313500298</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Martinez</t>
+          <t>Davis</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MD. Daniel Martinez</t>
+          <t>DO. Michael Davis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>INTERNAL MEDICINE</t>
+          <t>NEUROLOGY</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7024 Medical Blvd</t>
+          <t>9028 Health Dr</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>46421</t>
+          <t>38893</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -753,15 +753,15 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -778,27 +778,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1469319644</t>
+          <t>1914763202</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Robinson</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MD. John Miller</t>
+          <t>PA. Joseph Robinson</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9991 Medical Blvd</t>
+          <t>2715 Elm St</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Baltimore</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>65392</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -833,11 +833,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>T004</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -858,22 +858,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1414797776</t>
+          <t>1209747451</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Betty</t>
+          <t>David</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MD. Betty Harris</t>
+          <t>MD. David Wilson</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -883,27 +883,27 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>INTERNAL MEDICINE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6025 Park Rd</t>
+          <t>1619 Health Dr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>35203</t>
+          <t>22676</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -913,15 +913,15 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -938,52 +938,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1208449460</t>
+          <t>1883543540</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Hernandez</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NP. Daniel Williams</t>
+          <t>DO. Susan Hernandez</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FAMILY PRACTICE</t>
+          <t>GERIATRICS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6327 Medical Blvd</t>
+          <t>7627 Park Rd</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>69429</t>
+          <t>26361</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -993,11 +993,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1018,52 +1018,52 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1754049436</t>
+          <t>1488302652</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Christopher</t>
+          <t>Ashley</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MD. Christopher Young</t>
+          <t>DO. Ashley Jackson</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NEUROLOGY</t>
+          <t>PSYCHIATRY</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2903 Park Rd</t>
+          <t>9559 Oak Ave</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>42087</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1073,15 +1073,15 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1098,52 +1098,52 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1835098955</t>
+          <t>1349957310</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Lewis</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MD. Jennifer Harris</t>
+          <t>NP. Mary Lewis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>INTERNAL MEDICINE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5413 Maple Ave</t>
+          <t>1754 Health Dr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Fort Worth</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>17331</t>
+          <t>46434</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1153,15 +1153,15 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1178,52 +1178,52 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1709004943</t>
+          <t>1481469012</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Rodriguez</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PA. Linda Young</t>
+          <t>MD. Joseph Rodriguez</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NEUROLOGY</t>
+          <t>FAMILY PRACTICE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5255 Oak Ave</t>
+          <t>3532 Elm St</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Albuquerque</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NM</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>95909</t>
+          <t>44993</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1233,15 +1233,15 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1258,52 +1258,52 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1364814270</t>
+          <t>1781802744</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Wright</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PA. Sarah Jackson</t>
+          <t>DO. Daniel Wright</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>INTERNAL MEDICINE</t>
+          <t>CARDIOLOGY</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9297 Park Rd</t>
+          <t>2903 Park Rd</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>El Paso</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>44438</t>
+          <t>42087</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1313,15 +1313,15 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1338,27 +1338,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1647099690</t>
+          <t>1335809993</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Betty</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Robinson</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PA. Betty Robinson</t>
+          <t>MD. Jennifer Harris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1368,22 +1368,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8185 Main St</t>
+          <t>5413 Maple Ave</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>Fort Worth</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>16175</t>
+          <t>17331</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1393,15 +1393,15 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1418,52 +1418,52 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1168212356</t>
+          <t>1387484583</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sandra</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>DO. Sandra Brown</t>
+          <t>PA. Linda Young</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>FAMILY PRACTICE</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6404 Health Dr</t>
+          <t>1184 Oak Ave</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>88104</t>
+          <t>84341</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1498,42 +1498,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1831980933</t>
+          <t>1524806516</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PharmD. Joseph Thompson</t>
+          <t>MD. Mark Lee</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PharmD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>GERIATRICS</t>
+          <t>NEUROLOGY</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8897 Maple Ave</t>
+          <t>7617 Oak Ave</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>44973</t>
+          <t>44718</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1553,15 +1553,15 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1578,52 +1578,52 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1875340444</t>
+          <t>1902099969</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>John</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Rodriguez</t>
+          <t>Davis</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MD. Matthew Rodriguez</t>
+          <t>DO. John Davis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NEUROLOGY</t>
+          <t>PSYCHIATRY</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4415 Park Rd</t>
+          <t>9677 Health Dr</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>KY</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>33416</t>
+          <t>86484</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1633,15 +1633,15 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1658,52 +1658,52 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1313579170</t>
+          <t>1647099690</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>Thomas</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Wright</t>
-        </is>
-      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PA. Thomas Wright</t>
+          <t>PharmD. Richard Thomas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PharmD</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>PSYCHIATRY</t>
+          <t>INTERNAL MEDICINE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2604 Medical Blvd</t>
+          <t>8185 Main St</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>31174</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1713,15 +1713,15 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1120912992</t>
+          <t>1740389325</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Sandra</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hall</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>DO. Karen Hall</t>
+          <t>DO. Sandra Brown</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1763,27 +1763,27 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PSYCHIATRY</t>
+          <t>GERIATRICS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1932 Medical Blvd</t>
+          <t>1140 Health Dr</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>50306</t>
+          <t>60019</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1793,11 +1793,11 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1818,42 +1818,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1976198296</t>
+          <t>1112327652</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PA. Linda Johnson</t>
+          <t>MD. Lisa Harris</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>PSYCHIATRY</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1233 Maple Ave</t>
+          <t>1976 Elm St</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>79822</t>
+          <t>80381</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1873,15 +1873,15 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1666585408</t>
+          <t>1415143362</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1908,42 +1908,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NP. Matthew Jones</t>
+          <t>DO. Matthew Wilson</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>INTERNAL MEDICINE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7032 Oak Ave</t>
+          <t>7223 Oak Ave</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Baltimore</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>80686</t>
+          <t>69470</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1953,11 +1953,11 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1655742829</t>
+          <t>1918150683</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>James</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1993,37 +1993,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MD. Matthew Walker</t>
+          <t>NP. James Walker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NEUROLOGY</t>
+          <t>FAMILY PRACTICE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7497 Main St</t>
+          <t>3027 Park Rd</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>42493</t>
+          <t>23947</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2033,15 +2033,15 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2058,52 +2058,52 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1107721109</t>
+          <t>1753876785</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Sandra</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Rodriguez</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MD. Linda Williams</t>
+          <t>PA. Sandra Rodriguez</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>INTERNAL MEDICINE</t>
+          <t>CARDIOLOGY</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1263 Elm St</t>
+          <t>3358 Oak Ave</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>San Jose</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>92719</t>
+          <t>59009</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2113,11 +2113,11 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2138,52 +2138,52 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1355555531</t>
+          <t>1100614068</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Davis</t>
+          <t>Garcia</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PA. Mary Davis</t>
+          <t>PharmD. Matthew Garcia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PharmD</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>GERIATRICS</t>
+          <t>NEUROLOGY</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4662 Elm St</t>
+          <t>9913 Medical Blvd</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>73624</t>
+          <t>74042</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2193,15 +2193,15 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2218,27 +2218,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1360916298</t>
+          <t>1357109965</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>James</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Martinez</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>NP. Michael Martinez</t>
+          <t>MD. James Brown</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2248,22 +2248,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7849 Maple Ave</t>
+          <t>1049 Oak Ave</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>63354</t>
+          <t>84364</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2273,15 +2273,15 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2298,27 +2298,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1882839238</t>
+          <t>1916690353</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NP. Michael Brown</t>
+          <t>MD. Robert Williams</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2328,22 +2328,22 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>987 Elm St</t>
+          <t>8827 Maple Ave</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>KY</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>95649</t>
+          <t>26483</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2353,15 +2353,15 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2378,52 +2378,52 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1305718272</t>
+          <t>1384602384</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Christopher</t>
+          <t>John</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Lewis</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MD. Christopher Brown</t>
+          <t>PA. John Lewis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>NEUROLOGY</t>
+          <t>PSYCHIATRY</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3216 Park Rd</t>
+          <t>8745 Maple Ave</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>68800</t>
+          <t>89507</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2433,11 +2433,11 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2458,52 +2458,52 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1967607278</t>
+          <t>1865523129</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MD. John White</t>
+          <t>DO. Jessica Miller</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PSYCHIATRY</t>
+          <t>INTERNAL MEDICINE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>9116 Main St</t>
+          <t>5207 Health Dr</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>16630</t>
+          <t>98039</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2513,11 +2513,11 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>T004</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1536383774</t>
+          <t>1229927269</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2548,42 +2548,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Martinez</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MD. Christopher Martinez</t>
+          <t>PA. Christopher Thomas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PSYCHIATRY</t>
+          <t>GERIATRICS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8056 Health Dr</t>
+          <t>4161 Oak Ave</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Albuquerque</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>NM</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>38016</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2593,15 +2593,15 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2618,52 +2618,52 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1941889393</t>
+          <t>1336456621</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sandra</t>
+          <t>David</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MD. Sandra Jackson</t>
+          <t>DO. David Smith</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>NEUROLOGY</t>
+          <t>PSYCHIATRY</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>7554 Medical Blvd</t>
+          <t>217 Main St</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Fresno</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>65444</t>
+          <t>92719</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2673,15 +2673,15 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2698,52 +2698,52 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1418587604</t>
+          <t>1176082500</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Walker</t>
+          <t>Davis</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>DO. Daniel Walker</t>
+          <t>PA. Mary Davis</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>FAMILY PRACTICE</t>
+          <t>INTERNAL MEDICINE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3666 Main St</t>
+          <t>8523 Oak Ave</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>WI</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>85914</t>
+          <t>46500</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2753,15 +2753,15 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2778,52 +2778,52 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1639931481</t>
+          <t>1718702544</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Betty</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Martinez</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>NP. Betty Martinez</t>
+          <t>DO. Nancy Martin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PSYCHIATRY</t>
+          <t>FAMILY PRACTICE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8801 Oak Ave</t>
+          <t>7844 Oak Ave</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>71993</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -2858,22 +2858,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1228727266</t>
+          <t>1480424119</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MD. Thomas Williams</t>
+          <t>MD. Margaret White</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2883,27 +2883,27 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>INTERNAL MEDICINE</t>
+          <t>CARDIOLOGY</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9433 Oak Ave</t>
+          <t>7039 Health Dr</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Tucson</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>85880</t>
+          <t>71213</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2913,15 +2913,15 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2938,52 +2938,52 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1439699535</t>
+          <t>1165082363</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Sandra</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Walker</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MD. Lisa Johnson</t>
+          <t>NP. Sandra Walker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>FAMILY PRACTICE</t>
+          <t>NEUROLOGY</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4372 Oak Ave</t>
+          <t>6696 Elm St</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>97782</t>
+          <t>54473</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2993,15 +2993,15 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3018,22 +3018,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1439492674</t>
+          <t>1675832441</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Hernandez</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MD. Daniel Anderson</t>
+          <t>MD. Margaret Hernandez</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3043,27 +3043,27 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PSYCHIATRY</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1288 Main St</t>
+          <t>7450 Oak Ave</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>70068</t>
+          <t>65296</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3073,15 +3073,15 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3098,22 +3098,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1474745382</t>
+          <t>1575808013</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Robinson</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MD. Lisa Robinson</t>
+          <t>MD. Jennifer Wilson</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3123,27 +3123,27 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PSYCHIATRY</t>
+          <t>NEUROLOGY</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1227 Oak Ave</t>
+          <t>9116 Main St</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>58434</t>
+          <t>16630</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3153,15 +3153,15 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3178,52 +3178,52 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1108399996</t>
+          <t>1909134796</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Christopher</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Garcia</t>
+          <t>Martinez</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PA. Barbara Garcia</t>
+          <t>MD. Christopher Martinez</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>FAMILY PRACTICE</t>
+          <t>PSYCHIATRY</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>9186 Medical Blvd</t>
+          <t>3972 Oak Ave</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Albuquerque</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>NM</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>96951</t>
+          <t>63269</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3233,15 +3233,15 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3258,52 +3258,52 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1392431670</t>
+          <t>1276777762</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Patricia</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MD. Patricia King</t>
+          <t>PA. Sarah Martin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>INTERNAL MEDICINE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4716 Park Rd</t>
+          <t>6309 Main St</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>37607</t>
+          <t>61173</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3313,15 +3313,15 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3338,22 +3338,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1369639388</t>
+          <t>1554200826</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>William</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Wright</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>NP. Daniel Anderson</t>
+          <t>NP. William Wright</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>932 Main St</t>
+          <t>9205 Elm St</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>WI</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>93136</t>
+          <t>73788</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3393,15 +3393,15 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3418,22 +3418,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1273497327</t>
+          <t>1721890096</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>John</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MD. Jessica Young</t>
+          <t>MD. John Miller</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3443,27 +3443,27 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>NEUROLOGY</t>
+          <t>PSYCHIATRY</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>7339 Park Rd</t>
+          <t>8983 Main St</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>San Jose</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>66057</t>
+          <t>51104</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3473,11 +3473,11 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3498,22 +3498,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1138684919</t>
+          <t>1269042105</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MD. Karen Smith</t>
+          <t>MD. Mary Johnson</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3523,27 +3523,27 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>INTERNAL MEDICINE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6149 Park Rd</t>
+          <t>1031 Park Rd</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Denver</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>82420</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3553,15 +3553,15 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3578,52 +3578,52 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1325567963</t>
+          <t>1533550699</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Sandra</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Garcia</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MD. John White</t>
+          <t>DO. Sandra Garcia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>NEUROLOGY</t>
+          <t>FAMILY PRACTICE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4188 Elm St</t>
+          <t>2064 Park Rd</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>23473</t>
+          <t>42271</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3633,11 +3633,11 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3658,52 +3658,52 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1354194771</t>
+          <t>1805849060</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Susan</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Hall</t>
+          <t>Clark</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PA. Susan Hall</t>
+          <t>DO. Charles Clark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NEUROLOGY</t>
+          <t>CARDIOLOGY</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2762 Maple Ave</t>
+          <t>9662 Park Rd</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>33206</t>
+          <t>78522</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3713,15 +3713,15 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3738,22 +3738,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1386480450</t>
+          <t>1356287095</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>David</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Wright</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MD. Mark White</t>
+          <t>MD. David Wright</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3763,27 +3763,27 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>NEUROLOGY</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2708 Maple Ave</t>
+          <t>4451 Health Dr</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>24168</t>
+          <t>27154</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3793,11 +3793,11 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3818,42 +3818,42 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1427696198</t>
+          <t>1110002396</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Hernandez</t>
+          <t>Rodriguez</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PA. Richard Hernandez</t>
+          <t>MD. Nancy Rodriguez</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>PSYCHIATRY</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3828 Oak Ave</t>
+          <t>7608 Park Rd</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>San Jose</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>83792</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3873,15 +3873,15 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3898,22 +3898,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1788785773</t>
+          <t>1242224154</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Patricia</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MD. Nancy Miller</t>
+          <t>MD. Patricia Williams</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3923,27 +3923,27 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>GERIATRICS</t>
+          <t>NEUROLOGY</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8446 Health Dr</t>
+          <t>5818 Main St</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Fort Worth</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>99065</t>
+          <t>42018</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -3978,52 +3978,52 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1723403479</t>
+          <t>1855420240</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Martinez</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PA. Anthony Martinez</t>
+          <t>MD. Susan Taylor</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>PSYCHIATRY</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5056 Park Rd</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>PSYCHIATRY</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>4449 Main St</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>24208</t>
+          <t>95717</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4033,15 +4033,15 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4058,52 +4058,52 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1224173718</t>
+          <t>1812308209</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>NP. Lisa White</t>
+          <t>PA. Thomas Smith</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>NEUROLOGY</t>
+          <t>INTERNAL MEDICINE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6411 Park Rd</t>
+          <t>1797 Oak Ave</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Jacksonville</t>
+          <t>El Paso</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>34914</t>
+          <t>44664</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4113,15 +4113,15 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4138,52 +4138,52 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1491079829</t>
+          <t>1392431670</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Patricia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>King</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MD. William Johnson</t>
+          <t>NP. Patricia King</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>INTERNAL MEDICINE</t>
+          <t>GERIATRICS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>7166 Main St</t>
+          <t>4716 Park Rd</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Las Vegas</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>97062</t>
+          <t>37607</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4193,15 +4193,15 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1432091877</t>
+          <t>1642678844</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ashley</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4233,37 +4233,37 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MD. Ashley Anderson</t>
+          <t>NP. Daniel Anderson</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>GERIATRICS</t>
+          <t>PSYCHIATRY</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6791 Medical Blvd</t>
+          <t>8104 Medical Blvd</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>62743</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -4298,52 +4298,52 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1760904107</t>
+          <t>1103807155</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Rodriguez</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MD. Daniel Taylor</t>
+          <t>PA. Robert Rodriguez</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>NEUROLOGY</t>
+          <t>INTERNAL MEDICINE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>9424 Medical Blvd</t>
+          <t>5564 Maple Ave</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>63225</t>
+          <t>27146</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4353,15 +4353,15 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4378,52 +4378,52 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1802984810</t>
+          <t>1857704655</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Christopher</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MD. Karen Young</t>
+          <t>NP. Christopher Wilson</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>PSYCHIATRY</t>
+          <t>FAMILY PRACTICE</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>5379 Health Dr</t>
+          <t>7107 Park Rd</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>67905</t>
+          <t>11267</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4433,11 +4433,11 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4458,52 +4458,52 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1404713332</t>
+          <t>1685823118</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Patricia</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Lewis</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>DO. Joseph Lewis</t>
+          <t>NP. Patricia Williams</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>FAMILY PRACTICE</t>
+          <t>CARDIOLOGY</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>8545 Elm St</t>
+          <t>690 Maple Ave</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Fresno</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>92960</t>
+          <t>58393</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -4533,67 +4533,75 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HCO0001</t>
+          <t>HCP0051</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2459905654</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>1430989881</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Charles</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>City Medical Center</t>
+          <t>Martinez</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>City Medical Center</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
+          <t>MD. Charles Martinez</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>MULTI-SPECIALTY</t>
+          <t>NEUROLOGY</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1630 Hospital Way</t>
+          <t>6074 Maple Ave</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Nashville</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>40784</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>HCO</t>
+          <t>HCP</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -4605,67 +4613,75 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HCO0002</t>
+          <t>HCP0052</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2966040317</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>1479759538</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Regional Health System</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Regional Health System</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>NP. Mark Thomas</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>NP</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>MULTI-SPECIALTY</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>3362 Hospital Way</t>
+          <t>9273 Maple Ave</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>29313</t>
+          <t>63264</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>HCO</t>
+          <t>HCP</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4677,67 +4693,75 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HCO0003</t>
+          <t>HCP0053</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2362897676</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>1274484941</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Lisa</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>University Hospital</t>
+          <t>Walker</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>University Hospital</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
+          <t>PA. Lisa Walker</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>MULTI-SPECIALTY</t>
+          <t>NEUROLOGY</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>7884 Hospital Way</t>
+          <t>3000 Health Dr</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>90120</t>
+          <t>13248</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>HCO</t>
+          <t>HCP</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -4749,67 +4773,75 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HCO0004</t>
+          <t>HCP0054</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2545002643</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>1961393416</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Community Clinic Network</t>
+          <t>Walker</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Community Clinic Network</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
+          <t>MD. Jennifer Walker</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>MULTI-SPECIALTY</t>
+          <t>PSYCHIATRY</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>9531 Hospital Way</t>
+          <t>4165 Medical Blvd</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>35485</t>
+          <t>30866</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>HCO</t>
+          <t>HCP</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -4821,54 +4853,62 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HCO0005</t>
+          <t>HCP0055</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2529123992</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>1605399561</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Margaret</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Metro Healthcare Group</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Metro Healthcare Group</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
+          <t>MD. Margaret Lee</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>MULTI-SPECIALTY</t>
+          <t>INTERNAL MEDICINE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4097 Hospital Way</t>
+          <t>3744 Oak Ave</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>29342</t>
+          <t>70332</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>HCO</t>
+          <t>HCP</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4877,11 +4917,11 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -4893,70 +4933,4030 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>HCP0056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1339362341</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Susan</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>NP. Susan Taylor</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>NP</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>GERIATRICS</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>487 Elm St</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Albuquerque</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>35313</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>T006</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>4</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>HCP0057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1477040284</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PA. Richard Anderson</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>PSYCHIATRY</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>8446 Health Dr</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>99065</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>T006</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>5</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>HCP0058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1380477683</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Martinez</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PA. Anthony Martinez</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>INTERNAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>3025 Park Rd</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>44795</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>T006</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>2</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>HCP0059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1568574364</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Mary</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>MD. Mary Brown</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>FAMILY PRACTICE</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>8479 Main St</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Nashville</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>60488</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>T006</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>6</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>HCP0060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1101815992</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Robinson</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>MD. Mark Robinson</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CARDIOLOGY</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>8618 Maple Ave</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>80575</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>T006</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>7</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>HCP0061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1491079829</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Walker</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>NP. Nancy Walker</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>NP</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>7166 Main St</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Louisville</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>97062</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>T007</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>4</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>HCP0062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1872830248</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ashley</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>MD. Ashley Anderson</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ONCOLOGY</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>5020 Park Rd</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Nashville</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>50538</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>T007</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>2</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>HCP0063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1695295870</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>MD. Nancy White</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2185 Oak Ave</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>65108</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>T007</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>5</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>HCP0064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1760904107</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>NP. Nancy Jackson</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>NP</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>PSYCHIATRY</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>9424 Medical Blvd</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>El Paso</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>63225</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>T007</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>3</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>HCP0065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1561588882</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Young</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>MD. Karen Young</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>INTERNAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>9602 Park Rd</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>95813</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>T007</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>4</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>HCP0066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1648868899</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>MD. David Harris</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>GERIATRICS</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>7852 Maple Ave</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>32241</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>T007</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>4</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>HCP0067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1459905654</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>DO. Nancy Williams</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>PSYCHIATRY</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1630 Maple Ave</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>San Jose</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>40784</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>T007</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>10</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>HCP0068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1126226563</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PA. Nancy Taylor</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>INTERNAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>857 Oak Ave</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>72277</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>T007</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>3</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>HCP0069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1776205431</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Lisa</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Hernandez</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>MD. Lisa Hernandez</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>FAMILY PRACTICE</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>9531 Oak Ave</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Baltimore</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>60328</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>T007</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>7</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>HCP0070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1906341966</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>MD. Sarah Jackson</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>CARDIOLOGY</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>1846 Maple Ave</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>65724</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>T007</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>HCP0071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1598806645</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Linda</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Garcia</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PharmD. Linda Garcia</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>PharmD</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>922 Park Rd</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Milwaukee</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>42662</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>T008</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>9</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>HCP0072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1816806128</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ashley</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Hernandez</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>MD. Ashley Hernandez</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ONCOLOGY</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>8802 Park Rd</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>88047</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>T008</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>8</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>HCP0073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1558209399</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Hall</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>MD. David Hall</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>9076 Health Dr</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Fresno</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>30861</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>T008</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>9</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>HCP0074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1784683755</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Betty</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Hernandez</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>MD. Betty Hernandez</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>PSYCHIATRY</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4643 Maple Ave</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>78327</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>T008</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>4</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>HCP0075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1866162966</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>MD. Sarah Rodriguez</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>INTERNAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>4781 Oak Ave</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>45614</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>T008</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>2</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>HCP0076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1261953189</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>DO. David Anderson</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>GERIATRICS</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>3888 Health Dr</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Fresno</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>30028</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>T008</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>3</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>HCP0077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1682624278</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>MD. Daniel Miller</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>PSYCHIATRY</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>7733 Health Dr</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>18161</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>T008</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>6</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>HCP0078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1846812123</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Young</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>MD. Michael Young</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>INTERNAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>420 Maple Ave</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Columbus</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>85456</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>T008</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>10</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>HCP0079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1909037759</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PA. Richard Martin</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>FAMILY PRACTICE</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>6489 Maple Ave</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>64921</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>T008</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>5</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>HCP0080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1336801619</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Walker</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>DO. Karen Walker</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>CARDIOLOGY</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>8099 Oak Ave</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Louisville</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>45774</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>T008</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>10</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>HCP0081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1877583839</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>MD. Jessica Martin</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2804 Maple Ave</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>71261</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>T009</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>7</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>HCP0082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1735540030</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ashley</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Jones</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>DO. Ashley Jones</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>ONCOLOGY</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>9346 Elm St</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Nashville</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>13552</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>T009</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>7</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>HCP0083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1295130056</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Robert</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>MD. Robert Rodriguez</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>923 Medical Blvd</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Columbus</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>59689</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>T009</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>8</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>HCP0084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1398775766</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>MD. David Miller</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>PSYCHIATRY</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>7006 Medical Blvd</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>20735</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>T009</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>7</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>HCP0085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1340756713</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>DO. Sarah Smith</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>INTERNAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>1224 Maple Ave</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Louisville</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>95426</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>T009</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>6</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>HCP0086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1121882877</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Mary</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Hall</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>PA. Mary Hall</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>GERIATRICS</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2596 Oak Ave</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>26544</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>T009</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>4</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>HCP0087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1599326438</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Lewis</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>DO. Sarah Lewis</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>PSYCHIATRY</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>4298 Maple Ave</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>58351</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>T009</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>4</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>HCP0088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1935147672</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Clark</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>PharmD. Jennifer Clark</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>PharmD</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>INTERNAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2783 Medical Blvd</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Nashville</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>24168</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>T009</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>2</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>HCP0089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1525904456</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Charles</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>MD. Charles Smith</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>FAMILY PRACTICE</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>3349 Main St</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>87607</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>T009</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>7</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>HCP0090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1834717549</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Young</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>MD. Daniel Young</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>CARDIOLOGY</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>9937 Maple Ave</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Oklahoma City</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>25866</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>T009</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>5</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>HCP0091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1559967386</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Margaret</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Robinson</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>MD. Margaret Robinson</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>6171 Main St</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Milwaukee</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>76317</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>T010</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>9</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>HCP0092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1213321496</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Christopher</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>PA. Christopher Anderson</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ONCOLOGY</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>7202 Medical Blvd</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>93307</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>T010</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>8</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>HCP0093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1289125618</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Young</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>NP. Mark Young</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>NP</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>NEUROLOGY</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>8648 Elm St</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>45400</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>T010</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>7</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>HCP0094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1599154414</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Lisa</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Allen</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>DO. Lisa Allen</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>PSYCHIATRY</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>7236 Maple Ave</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>87656</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>T010</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>8</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>HCP0095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1399496923</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>MD. William Anderson</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>INTERNAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>7485 Oak Ave</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Tucson</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>70910</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>T010</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>2</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>HCP0096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1630757561</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Charles</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Clark</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>MD. Charles Clark</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>GERIATRICS</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>5425 Oak Ave</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>El Paso</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>73904</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>T010</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>1</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>HCP0097</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1740116562</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>MD. Michael Thomas</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>PSYCHIATRY</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>4626 Park Rd</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Milwaukee</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>11330</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>T010</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>5</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>HCP0098</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1624606470</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>MD. Thomas Miller</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>INTERNAL MEDICINE</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>9196 Maple Ave</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>41499</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>T010</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>7</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>HCP0099</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1951405188</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>NP. Daniel Martin</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>NP</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>FAMILY PRACTICE</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>382 Main St</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Oklahoma City</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>48566</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>T010</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>8</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>HCP0100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1496232693</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Linda</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>MD. Linda Jackson</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>CARDIOLOGY</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>7853 Park Rd</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Las Vegas</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>79588</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>T010</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>10</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>HCO0001</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2556881239</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>City Medical Center</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>City Medical Center</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>MULTI-SPECIALTY</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>9117 Hospital Way</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Jacksonville</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>53357</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>HCO</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>T002</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>9</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>HCO0002</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2587205269</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Regional Health System</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Regional Health System</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>MULTI-SPECIALTY</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>4538 Hospital Way</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Las Vegas</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>50189</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>HCO</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>T003</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>9</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>HCO0003</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2229553265</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>University Hospital</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>University Hospital</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>MULTI-SPECIALTY</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>3255 Hospital Way</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>51359</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>HCO</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>T004</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>7</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>HCO0004</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2675379544</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Community Clinic Network</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Community Clinic Network</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>MULTI-SPECIALTY</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>3133 Hospital Way</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Louisville</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>35105</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>HCO</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>T005</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>8</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>HCO0005</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2619904272</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Metro Healthcare Group</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Metro Healthcare Group</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>MULTI-SPECIALTY</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>4630 Hospital Way</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Louisville</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>87278</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>HCO</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>T006</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>9</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>HCO0006</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2906341966</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2994027897</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
         <is>
           <t>Wellness Medical Associates</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>Wellness Medical Associates</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
         <is>
           <t>MULTI-SPECIALTY</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>1846 Hospital Way</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Fresno</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>65724</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>3280 Hospital Way</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>48829</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
         <is>
           <t>HCO</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>T009</t>
-        </is>
-      </c>
-      <c r="N57" t="n">
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>T007</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
         <v>8</v>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="O107" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="P107" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
